--- a/Assets/GameData/Excel/windows.xlsx
+++ b/Assets/GameData/Excel/windows.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>windowId</t>
   </si>
@@ -68,13 +68,16 @@
     <t>MainWindow</t>
   </si>
   <si>
-    <t>Prefabs/Windows/main_window</t>
-  </si>
-  <si>
     <t>FadeIn</t>
   </si>
   <si>
     <t>FadeOut</t>
+  </si>
+  <si>
+    <t>loading_window</t>
+  </si>
+  <si>
+    <t>LoadingWindow</t>
   </si>
 </sst>
 </file>
@@ -740,8 +743,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,7 +761,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1106,87 +1112,94 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="21.3846153846154" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="25.7980769230769" customWidth="1"/>
-    <col min="4" max="4" width="15.8461538461538" customWidth="1"/>
-    <col min="5" max="5" width="20.2307692307692" customWidth="1"/>
-    <col min="6" max="6" width="15.8461538461538" customWidth="1"/>
-    <col min="7" max="7" width="20.2307692307692" customWidth="1"/>
-    <col min="8" max="8" width="20.6153846153846" customWidth="1"/>
-    <col min="9" max="9" width="23.1538461538462" customWidth="1"/>
+    <col min="1" max="1" width="21.3846153846154" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7980769230769" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.8461538461538" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.2307692307692" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.8461538461538" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.2307692307692" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6153846153846" style="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1538461538462" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="34" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="17" spans="1:9">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>0.2</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
